--- a/data/trans_orig/IP3105-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3105-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2007 (tasa de respuesta: 98,79%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2007 (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13576</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23053</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36461</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>47368</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62165</t>
+          <t>61657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63136</t>
+          <t>62869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103091</t>
+          <t>102067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>122248</t>
+          <t>122413</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>18813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46405</t>
+          <t>47723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43280</t>
+          <t>41982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64333</t>
+          <t>63864</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76167</t>
+          <t>76152</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>104747</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68541</t>
+          <t>67536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94721</t>
+          <t>95414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>82112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110444</t>
+          <t>111438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158656</t>
+          <t>158707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196650</t>
+          <t>196288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236064</t>
+          <t>235881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266455</t>
+          <t>266704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262450</t>
+          <t>261836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295147</t>
+          <t>294750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>508381</t>
+          <t>508214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>554147</t>
+          <t>554804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7365</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10724</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>22572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21851</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26562</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40676</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56183</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>79672</t>
+          <t>80592</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90745</t>
+          <t>90615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110147</t>
+          <t>110672</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80139</t>
+          <t>80266</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98604</t>
+          <t>99295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>176389</t>
+          <t>173892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>203181</t>
+          <t>202752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>18395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33811</t>
+          <t>33843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>27865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>26810</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29441</t>
+          <t>29187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48685</t>
+          <t>49748</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50256</t>
+          <t>50336</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>74879</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61475</t>
+          <t>62592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89419</t>
+          <t>88798</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>120756</t>
+          <t>118818</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>155236</t>
+          <t>154294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116234</t>
+          <t>115779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>148886</t>
+          <t>149588</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125494</t>
+          <t>126058</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>158863</t>
+          <t>158534</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>250650</t>
+          <t>249896</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>298057</t>
+          <t>298011</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>389610</t>
+          <t>386466</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>427272</t>
+          <t>428046</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>405184</t>
+          <t>404916</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>446382</t>
+          <t>442670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>805528</t>
+          <t>805481</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>860766</t>
+          <t>862212</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2012 (tasa de respuesta: 99,07%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2012 (tasa de respuesta: 99,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>11934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>23053</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17710</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15578</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>28825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>53473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67594</t>
+          <t>67591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51376</t>
+          <t>51570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65806</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>110087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130052</t>
+          <t>129157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>20720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33588</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31549</t>
+          <t>31095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49282</t>
+          <t>49277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36613</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40067</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>46034</t>
+          <t>46157</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71850</t>
+          <t>71101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>42922</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64434</t>
+          <t>64970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45630</t>
+          <t>45269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69044</t>
+          <t>67089</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94220</t>
+          <t>94146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125419</t>
+          <t>125629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>282106</t>
+          <t>280964</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313037</t>
+          <t>312340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320426</t>
+          <t>320287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>351180</t>
+          <t>351442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>612288</t>
+          <t>612051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>653960</t>
+          <t>653263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15311</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20221</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>18013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>34278</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25121</t>
+          <t>23816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105034</t>
+          <t>104492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123208</t>
+          <t>122511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109319</t>
+          <t>109239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>126587</t>
+          <t>126569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219119</t>
+          <t>219327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>243975</t>
+          <t>244385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,44%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28805</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27669</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>46834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>22843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>40946</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>19034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46371</t>
+          <t>45710</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71119</t>
+          <t>71174</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63569</t>
+          <t>64038</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>38241</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>59221</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>83215</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>115841</t>
+          <t>116658</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67200</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95719</t>
+          <t>96611</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71126</t>
+          <t>70123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97516</t>
+          <t>97764</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>145704</t>
+          <t>145052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184203</t>
+          <t>184941</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>454107</t>
+          <t>452969</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>490209</t>
+          <t>491484</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>495102</t>
+          <t>494946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>530656</t>
+          <t>531934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>958103</t>
+          <t>957831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1010227</t>
+          <t>1009923</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2016 (tasa de respuesta: 98,69%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2016 (tasa de respuesta: 98,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8187</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11133</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>25737</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24039</t>
+          <t>24012</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>20250</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35830</t>
+          <t>35900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>25301</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37157</t>
+          <t>37204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>33434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46997</t>
+          <t>46996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61787</t>
+          <t>62336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80426</t>
+          <t>80548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>23439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21678</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16710</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>40327</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61535</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38909</t>
+          <t>38804</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61232</t>
+          <t>61683</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85024</t>
+          <t>84764</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114772</t>
+          <t>115350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87508</t>
+          <t>86382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115776</t>
+          <t>114503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102884</t>
+          <t>103001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133830</t>
+          <t>135115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>198818</t>
+          <t>198284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>241280</t>
+          <t>240746</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244576</t>
+          <t>244298</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278172</t>
+          <t>278537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256714</t>
+          <t>257067</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>292492</t>
+          <t>291189</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>513730</t>
+          <t>515413</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561480</t>
+          <t>560468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26116</t>
+          <t>26915</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41043</t>
+          <t>41691</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>27023</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44617</t>
+          <t>44444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29986</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47475</t>
+          <t>48270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>61181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85255</t>
+          <t>86056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78085</t>
+          <t>79748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99394</t>
+          <t>99384</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97534</t>
+          <t>97605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117432</t>
+          <t>118533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182227</t>
+          <t>182051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>211329</t>
+          <t>210867</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35827</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17914</t>
+          <t>17823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>33928</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>24747</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>32280</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>95967</t>
+          <t>95979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56555</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82323</t>
+          <t>82574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>132399</t>
+          <t>131689</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170021</t>
+          <t>168947</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127409</t>
+          <t>128588</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162621</t>
+          <t>163246</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155417</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192881</t>
+          <t>194617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>297408</t>
+          <t>295819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>346836</t>
+          <t>348267</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>363198</t>
+          <t>363911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>403231</t>
+          <t>400941</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>402414</t>
+          <t>402076</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>444439</t>
+          <t>443818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>776806</t>
+          <t>776521</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>835638</t>
+          <t>836099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
